--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:52:28-05:00</t>
+    <t>2026-06-11T12:11:14-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T12:11:14-05:00</t>
+    <t>2026-06-12T09:38:46-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:38:46-05:00</t>
+    <t>2026-06-21T21:50:44-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T21:50:44-05:00</t>
+    <t>2026-06-21T22:38:39-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T22:38:39-05:00</t>
+    <t>2026-06-21T23:16:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T23:16:04-05:00</t>
+    <t>2026-06-22T08:51:47-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:51:47-05:00</t>
+    <t>2026-06-22T09:21:59-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:21:59-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T19:24:07-05:00</t>
+    <t>2026-08-18T15:36:33-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -338,7 +338,7 @@
     <t>US Core Race Extension</t>
   </si>
   <si>
-    <t>Concepts classifying the person into a named category of humans sharing common history, traits, geographical origin or nationality.  The race codes used to represent these concepts are based upon the [CDC Race and Ethnicity Code Set Version 1.0](http://www.cdc.gov/phin/resources/vocabulary/index.html) which includes over 900 concepts for representing race and ethnicity of which 921 reference race.  The race concepts are grouped by and pre-mapped to the 5 OMB race categories:
+    <t>Concepts classifying the person into a named category of humans sharing common history, traits, geographical origin or nationality.  The race codes used to represent these concepts are based upon the [Race &amp; Ethnicity - CDC (CDCREC)](https://phinvads.cdc.gov/vads/ViewCodeSystem.action?id=2.16.840.1.113883.6.238) code system. Detailed race concepts are grouped by and pre-mapped to the 5 OMB race categories:
    - American Indian or Alaska Native
    - Asian
    - Black or African American

--- a/build/output/StructureDefinition-cibmtr-ancestry.xlsx
+++ b/build/output/StructureDefinition-cibmtr-ancestry.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:36:33-05:00</t>
+    <t>2026-08-19T10:07:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
